--- a/correctionProfile/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:57:50+00:00</t>
+    <t>2026-09-17T15:33:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:33:46+00:00</t>
+    <t>2026-09-28T13:37:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:37:45+00:00</t>
+    <t>2026-09-29T08:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1116,7 +1116,7 @@
     <t>If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-human-substance-administration-site-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-human-substance-administration-site-cisis|20260916095453</t>
   </si>
   <si>
     <t>.approachSiteCode</t>

--- a/correctionProfile/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:08:01+00:00</t>
+    <t>2026-09-29T09:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:01:26+00:00</t>
+    <t>2026-09-30T14:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
